--- a/planning/acceptance-test-plan/atp_661_Dissonance.xlsx
+++ b/planning/acceptance-test-plan/atp_661_Dissonance.xlsx
@@ -440,7 +440,7 @@
 5. Re-import the file</t>
   </si>
   <si>
-    <t>Nothing is written while audio is playing. On pause the queued write is flushed and the new value is present after re-import.</t>
+    <t>Nothing is written while audio is playing. On pause the queued write is flushed and the new value is present after re-import. If the tester switches file during playback instead, playback stops and the pending edit is saved before the switch, as in F20.</t>
   </si>
   <si>
     <t>F20</t>
